--- a/data/trans_orig/IP1010-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248941</t>
+          <t>248852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248100</t>
+          <t>248329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499811</t>
+          <t>499685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505720</t>
+          <t>505737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264869</t>
+          <t>264813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201713</t>
+          <t>202063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395580</t>
+          <t>395536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676698</t>
+          <t>676661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713425</t>
+          <t>712767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720686</t>
+          <t>720693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393161</t>
+          <t>1393096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401086</t>
+          <t>1401003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229141</t>
+          <t>228093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>234036</t>
+          <t>234031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495456</t>
+          <t>495531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501131</t>
+          <t>501133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171999</t>
+          <t>171431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177315</t>
+          <t>177275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342735</t>
+          <t>343176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348636</t>
+          <t>348619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>700966</t>
+          <t>700500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706928</t>
+          <t>706485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741411</t>
+          <t>741797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747454</t>
+          <t>747456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445911</t>
+          <t>1445480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453079</t>
+          <t>1453105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178574</t>
+          <t>178255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186410</t>
+          <t>186434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367213</t>
+          <t>367326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375296</t>
+          <t>375333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170284</t>
+          <t>170058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345223</t>
+          <t>344710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701388</t>
+          <t>701773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734707</t>
+          <t>734287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742665</t>
+          <t>742673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438415</t>
+          <t>1439127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446572</t>
+          <t>1446657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1010-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5235</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6982</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251780</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>248521</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253154</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>251958</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>248852</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>249125</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251780</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248329</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253155</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>756</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499685</t>
+          <t>499979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505737</t>
+          <t>505720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1373</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140142</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136893</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140142</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136793</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264813</t>
+          <t>264210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,92 +1751,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1309</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3986</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204740</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201429</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204740</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202063</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395536</t>
+          <t>395537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,74 +2094,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>718042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>712871</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720694</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679774</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676661</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676644</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>718042</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>712767</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720693</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2095</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393096</t>
+          <t>1393079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401003</t>
+          <t>1401019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6383</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>232381</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>228093</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>234031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>228398</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>234034</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>705</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495531</t>
+          <t>496137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501133</t>
+          <t>501187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2649</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6526</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175308</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>171239</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176709</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175308</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171431</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177275</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343176</t>
+          <t>343066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348619</t>
+          <t>348610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6345</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>745493</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747492</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704833</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>700500</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>699827</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706485</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>745493</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741797</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747456</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2077</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445480</t>
+          <t>1445881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453105</t>
+          <t>1453298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,92 +5302,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9441</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>5057</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10317</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>183515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>179131</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>183515</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178255</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186434</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367326</t>
+          <t>367377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375333</t>
+          <t>375308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,92 +5645,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>172777</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>170058</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>170630</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>480</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344710</t>
+          <t>344703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10311</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>739787</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>734533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>742652</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703847</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701773</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701244</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>739787</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>734287</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>742673</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2118</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439127</t>
+          <t>1438214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446657</t>
+          <t>1446552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
